--- a/data/trans_dic/P64D$noloshace_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 11,36</t>
+          <t>4,63; 11,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,33</t>
+          <t>2,91; 7,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,23</t>
+          <t>4,4; 8,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 14,52</t>
+          <t>4,68; 13,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 11,5</t>
+          <t>5,09; 11,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,79</t>
+          <t>5,84; 11,22</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,66</t>
+          <t>0,14; 3,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,49</t>
+          <t>4,73; 15,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,83</t>
+          <t>0,56; 5,14</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,72</t>
+          <t>1,02; 3,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,18</t>
+          <t>1,0; 3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,91</t>
+          <t>1,3; 3,11</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,31</t>
+          <t>0,07; 1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,95</t>
+          <t>0,08; 0,89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,35; 4,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,63; 4,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,71; 4,42</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2,31; 4,8</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2,62; 4,57</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2,72; 4,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16765; 39853</t>
+          <t>16230; 38951</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8714; 22921</t>
+          <t>9104; 23539</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28753; 54619</t>
+          <t>29184; 58118</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14434; 44059</t>
+          <t>14191; 42040</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12701; 29006</t>
+          <t>12835; 28162</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31193; 59929</t>
+          <t>32425; 62342</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>214; 17931</t>
+          <t>676; 18889</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3537; 11339</t>
+          <t>3462; 11224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3947; 27198</t>
+          <t>3134; 28948</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5980; 20843</t>
+          <t>5703; 20313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4451; 13553</t>
+          <t>4248; 13057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12610; 28686</t>
+          <t>12815; 30643</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4760</t>
+          <t>0; 4464</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>234; 4874</t>
+          <t>259; 4753</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>625; 5807</t>
+          <t>478; 5462</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70666</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49857</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120523</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45657; 96655</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37781; 64557</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91765; 149389</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>70666</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>49857</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>120523</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>44818; 93349</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>37620; 65761</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>91969; 151077</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P64D$noloshace_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,1</t>
+          <t>5,6; 12,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,53</t>
+          <t>3,45; 7,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,76</t>
+          <t>5,48; 10,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,86</t>
+          <t>4,57; 12,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,17</t>
+          <t>5,14; 11,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,22</t>
+          <t>5,65; 10,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,86</t>
+          <t>1,25; 5,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 15,33</t>
+          <t>5,49; 17,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,14</t>
+          <t>2,7; 7,07</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,63</t>
+          <t>1,14; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,06</t>
+          <t>1,1; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,11</t>
+          <t>1,4; 3,16</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,27</t>
+          <t>0,24; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,89</t>
+          <t>0,34; 1,89</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,97</t>
+          <t>3,35; 5,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,49</t>
+          <t>3,26; 5,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,42</t>
+          <t>3,55; 5,07</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26659</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41219</t>
+          <t>52444</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16230; 38951</t>
+          <t>21378; 48677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9104; 23539</t>
+          <t>11506; 26544</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29184; 58118</t>
+          <t>39153; 71961</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43560</t>
+          <t>45209</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14191; 42040</t>
+          <t>14653; 39029</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12835; 28162</t>
+          <t>14049; 31833</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32425; 62342</t>
+          <t>33578; 62422</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>16156</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>676; 18889</t>
+          <t>3404; 16025</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3462; 11224</t>
+          <t>4551; 14470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3134; 28948</t>
+          <t>9565; 25056</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>23391</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5703; 20313</t>
+          <t>7097; 22967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4248; 13057</t>
+          <t>5250; 16117</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12815; 30643</t>
+          <t>15368; 34750</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>5411</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4464</t>
+          <t>0; 7457</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>259; 4753</t>
+          <t>740; 7967</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>478; 5462</t>
+          <t>2109; 11738</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>70666</t>
+          <t>82154</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120523</t>
+          <t>142611</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45657; 96655</t>
+          <t>63672; 105563</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37781; 64557</t>
+          <t>48221; 74898</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91765; 149389</t>
+          <t>120245; 171595</t>
         </is>
       </c>
     </row>
